--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2023_T2_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2023_T2_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>50</t>
+    <t>56</t>
+  </si>
+  <si>
+    <t>55</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,67 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.27e+05</t>
-  </si>
-  <si>
-    <t>(86461.590)</t>
-  </si>
-  <si>
-    <t>507.992</t>
-  </si>
-  <si>
-    <t>(37.599)</t>
-  </si>
-  <si>
-    <t>3.745</t>
-  </si>
-  <si>
-    <t>(0.050)</t>
-  </si>
-  <si>
-    <t>5.235</t>
-  </si>
-  <si>
-    <t>(1.233)</t>
-  </si>
-  <si>
-    <t>86.670</t>
-  </si>
-  <si>
-    <t>(0.525)</t>
-  </si>
-  <si>
-    <t>8.70e+05</t>
-  </si>
-  <si>
-    <t>(57542.177)</t>
-  </si>
-  <si>
-    <t>2.074</t>
-  </si>
-  <si>
-    <t>(0.140)</t>
-  </si>
-  <si>
-    <t>2.118</t>
-  </si>
-  <si>
-    <t>(0.425)</t>
-  </si>
-  <si>
-    <t>29.196</t>
-  </si>
-  <si>
-    <t>(4.922)</t>
-  </si>
-  <si>
-    <t>0.922</t>
-  </si>
-  <si>
-    <t>(0.038)</t>
-  </si>
-  <si>
-    <t>65</t>
+    <t>5.24e+05</t>
+  </si>
+  <si>
+    <t>(80953.804)</t>
+  </si>
+  <si>
+    <t>503.534</t>
+  </si>
+  <si>
+    <t>(38.331)</t>
+  </si>
+  <si>
+    <t>3.714</t>
+  </si>
+  <si>
+    <t>(0.049)</t>
+  </si>
+  <si>
+    <t>6.411</t>
+  </si>
+  <si>
+    <t>(1.336)</t>
+  </si>
+  <si>
+    <t>87.003</t>
+  </si>
+  <si>
+    <t>(0.512)</t>
+  </si>
+  <si>
+    <t>8.97e+05</t>
+  </si>
+  <si>
+    <t>(55836.359)</t>
+  </si>
+  <si>
+    <t>2.162</t>
+  </si>
+  <si>
+    <t>(0.135)</t>
+  </si>
+  <si>
+    <t>2.339</t>
+  </si>
+  <si>
+    <t>(0.404)</t>
+  </si>
+  <si>
+    <t>29.286</t>
+  </si>
+  <si>
+    <t>(4.490)</t>
+  </si>
+  <si>
+    <t>0.929</t>
+  </si>
+  <si>
+    <t>(0.035)</t>
+  </si>
+  <si>
+    <t>60</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -141,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>6.82e+05</t>
-  </si>
-  <si>
-    <t>(94287.169)</t>
-  </si>
-  <si>
-    <t>480.586</t>
-  </si>
-  <si>
-    <t>(43.051)</t>
-  </si>
-  <si>
-    <t>3.340</t>
-  </si>
-  <si>
-    <t>(0.046)</t>
-  </si>
-  <si>
-    <t>24.492</t>
-  </si>
-  <si>
-    <t>(2.985)</t>
-  </si>
-  <si>
-    <t>91.425</t>
-  </si>
-  <si>
-    <t>(0.354)</t>
-  </si>
-  <si>
-    <t>1.36e+06</t>
-  </si>
-  <si>
-    <t>(54825.632)</t>
-  </si>
-  <si>
-    <t>3.328</t>
-  </si>
-  <si>
-    <t>(0.112)</t>
-  </si>
-  <si>
-    <t>5.954</t>
-  </si>
-  <si>
-    <t>(0.507)</t>
-  </si>
-  <si>
-    <t>43.123</t>
-  </si>
-  <si>
-    <t>(2.583)</t>
+    <t>6.98e+05</t>
+  </si>
+  <si>
+    <t>(1.00e+05)</t>
+  </si>
+  <si>
+    <t>482.463</t>
+  </si>
+  <si>
+    <t>(43.823)</t>
+  </si>
+  <si>
+    <t>3.335</t>
+  </si>
+  <si>
+    <t>(0.048)</t>
+  </si>
+  <si>
+    <t>25.000</t>
+  </si>
+  <si>
+    <t>(3.191)</t>
+  </si>
+  <si>
+    <t>91.511</t>
+  </si>
+  <si>
+    <t>(0.367)</t>
+  </si>
+  <si>
+    <t>1.38e+06</t>
+  </si>
+  <si>
+    <t>(57218.217)</t>
+  </si>
+  <si>
+    <t>3.352</t>
+  </si>
+  <si>
+    <t>(0.119)</t>
+  </si>
+  <si>
+    <t>6.067</t>
+  </si>
+  <si>
+    <t>(0.544)</t>
+  </si>
+  <si>
+    <t>44.200</t>
+  </si>
+  <si>
+    <t>(2.738)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.55e+05</t>
-  </si>
-  <si>
-    <t>-27.406</t>
-  </si>
-  <si>
-    <t>-0.405***</t>
-  </si>
-  <si>
-    <t>19.257***</t>
-  </si>
-  <si>
-    <t>4.755***</t>
-  </si>
-  <si>
-    <t>4.94e+05***</t>
-  </si>
-  <si>
-    <t>1.254***</t>
-  </si>
-  <si>
-    <t>3.836***</t>
-  </si>
-  <si>
-    <t>13.927***</t>
-  </si>
-  <si>
-    <t>0.078**</t>
+    <t>1.74e+05</t>
+  </si>
+  <si>
+    <t>-21.071</t>
+  </si>
+  <si>
+    <t>-0.380***</t>
+  </si>
+  <si>
+    <t>18.589***</t>
+  </si>
+  <si>
+    <t>4.508***</t>
+  </si>
+  <si>
+    <t>4.82e+05***</t>
+  </si>
+  <si>
+    <t>1.190***</t>
+  </si>
+  <si>
+    <t>3.727***</t>
+  </si>
+  <si>
+    <t>14.914***</t>
+  </si>
+  <si>
+    <t>0.071**</t>
   </si>
 </sst>
 </file>

--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2023_T2_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2023_T2_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>55</t>
+    <t>51</t>
+  </si>
+  <si>
+    <t>50</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,67 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.24e+05</t>
-  </si>
-  <si>
-    <t>(80953.804)</t>
-  </si>
-  <si>
-    <t>503.534</t>
-  </si>
-  <si>
-    <t>(38.331)</t>
-  </si>
-  <si>
-    <t>3.714</t>
-  </si>
-  <si>
-    <t>(0.049)</t>
-  </si>
-  <si>
-    <t>6.411</t>
-  </si>
-  <si>
-    <t>(1.336)</t>
-  </si>
-  <si>
-    <t>87.003</t>
-  </si>
-  <si>
-    <t>(0.512)</t>
-  </si>
-  <si>
-    <t>8.97e+05</t>
-  </si>
-  <si>
-    <t>(55836.359)</t>
-  </si>
-  <si>
-    <t>2.162</t>
-  </si>
-  <si>
-    <t>(0.135)</t>
-  </si>
-  <si>
-    <t>2.339</t>
-  </si>
-  <si>
-    <t>(0.404)</t>
-  </si>
-  <si>
-    <t>29.286</t>
-  </si>
-  <si>
-    <t>(4.490)</t>
-  </si>
-  <si>
-    <t>0.929</t>
-  </si>
-  <si>
-    <t>(0.035)</t>
-  </si>
-  <si>
-    <t>60</t>
+    <t>5.27e+05</t>
+  </si>
+  <si>
+    <t>(86461.590)</t>
+  </si>
+  <si>
+    <t>507.992</t>
+  </si>
+  <si>
+    <t>(37.599)</t>
+  </si>
+  <si>
+    <t>3.745</t>
+  </si>
+  <si>
+    <t>(0.050)</t>
+  </si>
+  <si>
+    <t>5.235</t>
+  </si>
+  <si>
+    <t>(1.233)</t>
+  </si>
+  <si>
+    <t>86.670</t>
+  </si>
+  <si>
+    <t>(0.525)</t>
+  </si>
+  <si>
+    <t>8.70e+05</t>
+  </si>
+  <si>
+    <t>(57542.177)</t>
+  </si>
+  <si>
+    <t>2.074</t>
+  </si>
+  <si>
+    <t>(0.140)</t>
+  </si>
+  <si>
+    <t>2.118</t>
+  </si>
+  <si>
+    <t>(0.425)</t>
+  </si>
+  <si>
+    <t>29.196</t>
+  </si>
+  <si>
+    <t>(4.922)</t>
+  </si>
+  <si>
+    <t>0.922</t>
+  </si>
+  <si>
+    <t>(0.038)</t>
+  </si>
+  <si>
+    <t>65</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -141,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>6.98e+05</t>
-  </si>
-  <si>
-    <t>(1.00e+05)</t>
-  </si>
-  <si>
-    <t>482.463</t>
-  </si>
-  <si>
-    <t>(43.823)</t>
-  </si>
-  <si>
-    <t>3.335</t>
-  </si>
-  <si>
-    <t>(0.048)</t>
-  </si>
-  <si>
-    <t>25.000</t>
-  </si>
-  <si>
-    <t>(3.191)</t>
-  </si>
-  <si>
-    <t>91.511</t>
-  </si>
-  <si>
-    <t>(0.367)</t>
-  </si>
-  <si>
-    <t>1.38e+06</t>
-  </si>
-  <si>
-    <t>(57218.217)</t>
-  </si>
-  <si>
-    <t>3.352</t>
-  </si>
-  <si>
-    <t>(0.119)</t>
-  </si>
-  <si>
-    <t>6.067</t>
-  </si>
-  <si>
-    <t>(0.544)</t>
-  </si>
-  <si>
-    <t>44.200</t>
-  </si>
-  <si>
-    <t>(2.738)</t>
+    <t>6.82e+05</t>
+  </si>
+  <si>
+    <t>(94287.169)</t>
+  </si>
+  <si>
+    <t>480.586</t>
+  </si>
+  <si>
+    <t>(43.051)</t>
+  </si>
+  <si>
+    <t>3.340</t>
+  </si>
+  <si>
+    <t>(0.046)</t>
+  </si>
+  <si>
+    <t>24.492</t>
+  </si>
+  <si>
+    <t>(2.985)</t>
+  </si>
+  <si>
+    <t>91.425</t>
+  </si>
+  <si>
+    <t>(0.354)</t>
+  </si>
+  <si>
+    <t>1.36e+06</t>
+  </si>
+  <si>
+    <t>(54825.632)</t>
+  </si>
+  <si>
+    <t>3.328</t>
+  </si>
+  <si>
+    <t>(0.112)</t>
+  </si>
+  <si>
+    <t>5.954</t>
+  </si>
+  <si>
+    <t>(0.507)</t>
+  </si>
+  <si>
+    <t>43.123</t>
+  </si>
+  <si>
+    <t>(2.583)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.74e+05</t>
-  </si>
-  <si>
-    <t>-21.071</t>
-  </si>
-  <si>
-    <t>-0.380***</t>
-  </si>
-  <si>
-    <t>18.589***</t>
-  </si>
-  <si>
-    <t>4.508***</t>
-  </si>
-  <si>
-    <t>4.82e+05***</t>
-  </si>
-  <si>
-    <t>1.190***</t>
-  </si>
-  <si>
-    <t>3.727***</t>
-  </si>
-  <si>
-    <t>14.914***</t>
-  </si>
-  <si>
-    <t>0.071**</t>
+    <t>1.55e+05</t>
+  </si>
+  <si>
+    <t>-27.406</t>
+  </si>
+  <si>
+    <t>-0.405***</t>
+  </si>
+  <si>
+    <t>19.257***</t>
+  </si>
+  <si>
+    <t>4.755***</t>
+  </si>
+  <si>
+    <t>4.94e+05***</t>
+  </si>
+  <si>
+    <t>1.254***</t>
+  </si>
+  <si>
+    <t>3.836***</t>
+  </si>
+  <si>
+    <t>13.927***</t>
+  </si>
+  <si>
+    <t>0.078**</t>
   </si>
 </sst>
 </file>
